--- a/artfynd/A 14301-2023 artfynd.xlsx
+++ b/artfynd/A 14301-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14301-2023 artfynd.xlsx
+++ b/artfynd/A 14301-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107856371</v>
+        <v>107773000</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585757.3301987207</v>
+        <v>585786</v>
       </c>
       <c r="R2" t="n">
-        <v>6393981.30443168</v>
+        <v>6394075</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,22 +747,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Utbredd undersidan av granlåga.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,47 +785,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107856613</v>
+        <v>107773230</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585871.3090144017</v>
+        <v>585753</v>
       </c>
       <c r="R3" t="n">
-        <v>6393989.072683465</v>
+        <v>6394102</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +894,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>107856240</v>
+        <v>107773154</v>
       </c>
       <c r="B4" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -969,13 +941,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585839.5429383111</v>
+        <v>585816</v>
       </c>
       <c r="R4" t="n">
-        <v>6393945.609328114</v>
+        <v>6394052</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,22 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,12 +1007,7 @@
         <v>107856215</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585827.0278735023</v>
+        <v>585827</v>
       </c>
       <c r="R5" t="n">
-        <v>6393929.297724779</v>
+        <v>6393929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,19 +1076,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,15 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>107856294</v>
+        <v>107856259</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585820.3320085882</v>
+        <v>585839</v>
       </c>
       <c r="R6" t="n">
-        <v>6393992.268917265</v>
+        <v>6393954</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,19 +1182,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1283,12 +1215,7 @@
         <v>107856266</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1332,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585831.1129932627</v>
+        <v>585831</v>
       </c>
       <c r="R7" t="n">
-        <v>6393989.288691249</v>
+        <v>6393989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1365,19 +1292,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,41 +1322,40 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107856305</v>
+        <v>107856294</v>
       </c>
       <c r="B8" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -1449,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585775.987021131</v>
+        <v>585820</v>
       </c>
       <c r="R8" t="n">
-        <v>6393985.979127978</v>
+        <v>6393992</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,19 +1398,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,15 +1428,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>107856259</v>
+        <v>107856335</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1456,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1570,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585838.8369974099</v>
+        <v>585761</v>
       </c>
       <c r="R9" t="n">
-        <v>6393953.617245103</v>
+        <v>6393944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1603,19 +1508,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,37 +1538,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107856280</v>
+        <v>107856371</v>
       </c>
       <c r="B10" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585819.2153204344</v>
+        <v>585757</v>
       </c>
       <c r="R10" t="n">
-        <v>6393994.384627678</v>
+        <v>6393981</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,19 +1614,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1764,15 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107856335</v>
+        <v>107856401</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1674,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1816,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585760.7910471369</v>
+        <v>585761</v>
       </c>
       <c r="R11" t="n">
-        <v>6393944.472637209</v>
+        <v>6394011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,19 +1724,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,15 +1754,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107856458</v>
+        <v>107856426</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1937,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585743.6268455352</v>
+        <v>585753</v>
       </c>
       <c r="R12" t="n">
-        <v>6394046.265612069</v>
+        <v>6394014</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,19 +1830,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,15 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107856401</v>
+        <v>107856458</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2043,11 +1888,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2062,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585760.9801785109</v>
+        <v>585744</v>
       </c>
       <c r="R13" t="n">
-        <v>6394011.333683502</v>
+        <v>6394046</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2095,19 +1936,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2135,15 +1966,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107856426</v>
+        <v>107856613</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2183,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585752.8775129406</v>
+        <v>585871</v>
       </c>
       <c r="R14" t="n">
-        <v>6394014.370892485</v>
+        <v>6393989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2216,19 +2042,9 @@
           <t>2023-04-05</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-05</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2253,6 +2069,642 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>107856681</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 14301, Dockrössle, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>586015</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6394018</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>107856708</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>A 14301, Dockrössle, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>586008</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6394020</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>107856751</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>A 14301, Dockrössle, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>586005</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6394014</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>107856240</v>
+      </c>
+      <c r="B18" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>A 14301, Dockrössle, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>585840</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6393946</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>107856280</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 14301, Dockrössle, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>585819</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6393994</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>107856305</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 14301, Dockrössle, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>585776</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6393986</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-04-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
